--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abmosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C0095E-ECFE-FA42-9CA1-D0E06A14B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903A7E8-EDF8-B649-865B-19AF3E455FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -456,10 +456,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -730,7 +730,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="54"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="25" t="s">
         <v>13</v>
       </c>
@@ -766,7 +766,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="54"/>
+      <c r="C5" s="53"/>
       <c r="D5" s="25" t="s">
         <v>13</v>
       </c>
@@ -803,7 +803,7 @@
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="C7" s="54"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="25" t="s">
         <v>13</v>
       </c>
@@ -843,7 +843,7 @@
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="53"/>
       <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
@@ -881,7 +881,7 @@
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="54"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="44" t="s">
         <v>13</v>
       </c>
@@ -923,7 +923,7 @@
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="54"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="25" t="s">
         <v>13</v>
       </c>
@@ -958,7 +958,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="54"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="25" t="s">
         <v>13</v>
       </c>
@@ -991,7 +991,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="54"/>
+      <c r="C17" s="53"/>
       <c r="D17" s="25" t="s">
         <v>13</v>
       </c>
@@ -1004,8 +1004,12 @@
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A18" s="18"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="C18" s="52">
         <v>9</v>
       </c>
@@ -1028,7 +1032,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="53"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="37" t="s">
         <v>13</v>
       </c>
@@ -1066,7 +1070,7 @@
     <row r="21" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="53"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="37" t="s">
         <v>13</v>
       </c>
@@ -1102,7 +1106,7 @@
       <c r="B23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="53"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="37" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1120,12 @@
       <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A24" s="18"/>
-      <c r="B24" s="15"/>
+      <c r="A24" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="C24" s="52">
         <v>12</v>
       </c>
@@ -1144,7 +1152,7 @@
       <c r="B25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="53"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="32" t="s">
         <v>13</v>
       </c>
@@ -1180,7 +1188,7 @@
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="20"/>
-      <c r="C27" s="53"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="37" t="s">
         <v>13</v>
       </c>
@@ -1216,7 +1224,7 @@
       <c r="B29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="53"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="37" t="s">
         <v>13</v>
       </c>
@@ -1256,7 +1264,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="53"/>
+      <c r="C31" s="54"/>
       <c r="D31" s="41"/>
       <c r="E31" s="38"/>
       <c r="F31" s="20" t="s">
@@ -1270,12 +1278,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1285,6 +1287,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903A7E8-EDF8-B649-865B-19AF3E455FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8B09D2-FB04-2E4D-82E8-B7475B462DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -136,24 +136,12 @@
     <t>Physical Viewing</t>
   </si>
   <si>
-    <t>Spatial Data Visualization</t>
-  </si>
-  <si>
-    <t>Text Data Visualization</t>
-  </si>
-  <si>
-    <t>Network Data Visualization</t>
-  </si>
-  <si>
     <t>Final Demonstrations</t>
   </si>
   <si>
     <t>Flex Day for Mountain Day</t>
   </si>
   <si>
-    <t>Flex Day - Make up or project workshop</t>
-  </si>
-  <si>
     <t>Flex Day - Make up or review</t>
   </si>
   <si>
@@ -203,6 +191,12 @@
   </si>
   <si>
     <t xml:space="preserve">Finals Period -- Final grade consultations </t>
+  </si>
+  <si>
+    <t>Applications: Preparation</t>
+  </si>
+  <si>
+    <t>Applications: Demos</t>
   </si>
 </sst>
 </file>
@@ -741,7 +735,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H3" s="27"/>
     </row>
@@ -777,10 +771,10 @@
         <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -814,10 +808,10 @@
         <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -851,7 +845,7 @@
         <v>46295</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="29"/>
@@ -892,10 +886,10 @@
         <v>23</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H11" s="47" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -934,7 +928,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
@@ -1023,10 +1017,10 @@
         <v>29</v>
       </c>
       <c r="G18" s="50" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H18" s="51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1063,7 +1057,7 @@
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="28" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I20" s="8"/>
     </row>
@@ -1114,7 +1108,7 @@
         <v>46344</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="39"/>
@@ -1139,10 +1133,10 @@
         <v>33</v>
       </c>
       <c r="G24" s="50" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H24" s="51" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1178,11 +1172,11 @@
         <v>46356</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="28" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1196,7 +1190,7 @@
         <v>46358</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="39"/>
@@ -1214,16 +1208,14 @@
         <v>46363</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="24"/>
     </row>
     <row r="29" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
-      <c r="B29" s="20" t="s">
-        <v>5</v>
-      </c>
+      <c r="B29" s="20"/>
       <c r="C29" s="54"/>
       <c r="D29" s="37" t="s">
         <v>13</v>
@@ -1231,8 +1223,8 @@
       <c r="E29" s="38">
         <v>46365</v>
       </c>
-      <c r="F29" s="40" t="s">
-        <v>39</v>
+      <c r="F29" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="39"/>
@@ -1254,11 +1246,11 @@
         <v>46370</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G30" s="50"/>
       <c r="H30" s="51" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1268,7 +1260,7 @@
       <c r="D31" s="41"/>
       <c r="E31" s="38"/>
       <c r="F31" s="20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G31" s="42"/>
       <c r="H31" s="39"/>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8B09D2-FB04-2E4D-82E8-B7475B462DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D1041-29EE-E644-978D-03305BB168A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,10 +450,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -724,7 +724,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="53"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="25" t="s">
         <v>13</v>
       </c>
@@ -760,7 +760,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="53"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="25" t="s">
         <v>13</v>
       </c>
@@ -790,14 +790,14 @@
         <v>46286</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="C7" s="53"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="25" t="s">
         <v>13</v>
       </c>
@@ -805,7 +805,7 @@
         <v>46288</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>39</v>
@@ -837,7 +837,7 @@
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="53"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
@@ -875,7 +875,7 @@
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="53"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="44" t="s">
         <v>13</v>
       </c>
@@ -917,7 +917,7 @@
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="53"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="25" t="s">
         <v>13</v>
       </c>
@@ -952,7 +952,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="53"/>
+      <c r="C15" s="54"/>
       <c r="D15" s="25" t="s">
         <v>13</v>
       </c>
@@ -985,7 +985,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="53"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="25" t="s">
         <v>13</v>
       </c>
@@ -1026,7 +1026,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="54"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="37" t="s">
         <v>13</v>
       </c>
@@ -1064,7 +1064,7 @@
     <row r="21" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="54"/>
+      <c r="C21" s="53"/>
       <c r="D21" s="37" t="s">
         <v>13</v>
       </c>
@@ -1100,7 +1100,7 @@
       <c r="B23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="54"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="37" t="s">
         <v>13</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="B25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="54"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="32" t="s">
         <v>13</v>
       </c>
@@ -1182,7 +1182,7 @@
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="20"/>
-      <c r="C27" s="54"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="37" t="s">
         <v>13</v>
       </c>
@@ -1216,7 +1216,7 @@
     <row r="29" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="54"/>
+      <c r="C29" s="53"/>
       <c r="D29" s="37" t="s">
         <v>13</v>
       </c>
@@ -1256,7 +1256,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="54"/>
+      <c r="C31" s="53"/>
       <c r="D31" s="41"/>
       <c r="E31" s="38"/>
       <c r="F31" s="20" t="s">
@@ -1270,6 +1270,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1279,12 +1285,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/website-SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D1041-29EE-E644-978D-03305BB168A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9743D8-50DA-704E-BECB-441F13BEA724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Final Demonstrations</t>
   </si>
   <si>
-    <t>Flex Day for Mountain Day</t>
-  </si>
-  <si>
     <t>Flex Day - Make up or review</t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>Applications: Demos</t>
+  </si>
+  <si>
+    <t>NO CLASS -MOUNTAIN DAY</t>
   </si>
 </sst>
 </file>
@@ -368,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -434,7 +434,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -450,12 +449,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,7 +718,7 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="14"/>
       <c r="B2" s="15"/>
-      <c r="C2" s="52">
+      <c r="C2" s="51">
         <v>1</v>
       </c>
       <c r="D2" s="22"/>
@@ -724,7 +730,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="54"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="25" t="s">
         <v>13</v>
       </c>
@@ -735,14 +741,14 @@
         <v>10</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="18"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="52">
+      <c r="C4" s="51">
         <v>2</v>
       </c>
       <c r="D4" s="22" t="s">
@@ -760,7 +766,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="54"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="25" t="s">
         <v>13</v>
       </c>
@@ -771,16 +777,16 @@
         <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="18"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="52">
+      <c r="C6" s="51">
         <v>3</v>
       </c>
       <c r="D6" s="22" t="s">
@@ -796,28 +802,33 @@
       <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="26">
+      <c r="A7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="55">
         <v>46288</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>44</v>
+      <c r="F7" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="18"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="52">
+      <c r="C8" s="51">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
@@ -827,25 +838,23 @@
         <v>46293</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G8" s="15"/>
       <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
-      <c r="B9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="54"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="26">
         <v>46295</v>
       </c>
-      <c r="F9" s="43" t="s">
-        <v>35</v>
+      <c r="F9" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="29"/>
@@ -853,7 +862,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="14"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="52">
+      <c r="C10" s="51">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
@@ -875,21 +884,21 @@
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="45">
+      <c r="C11" s="52"/>
+      <c r="D11" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="44">
         <v>46302</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="47" t="s">
-        <v>45</v>
+      <c r="G11" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="46" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -899,7 +908,7 @@
       <c r="B12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="51">
         <v>6</v>
       </c>
       <c r="D12" s="11" t="s">
@@ -917,7 +926,7 @@
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="54"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="25" t="s">
         <v>13</v>
       </c>
@@ -928,13 +937,13 @@
         <v>24</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="14"/>
       <c r="B14" s="15"/>
-      <c r="C14" s="52">
+      <c r="C14" s="51">
         <v>7</v>
       </c>
       <c r="D14" s="22" t="s">
@@ -952,7 +961,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="54"/>
+      <c r="C15" s="52"/>
       <c r="D15" s="25" t="s">
         <v>13</v>
       </c>
@@ -967,7 +976,7 @@
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="14"/>
       <c r="B16" s="15"/>
-      <c r="C16" s="52">
+      <c r="C16" s="51">
         <v>8</v>
       </c>
       <c r="D16" s="22" t="s">
@@ -985,7 +994,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="54"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="25" t="s">
         <v>13</v>
       </c>
@@ -1004,23 +1013,23 @@
       <c r="B18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="51">
         <v>9</v>
       </c>
-      <c r="D18" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="49">
+      <c r="D18" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="48">
         <v>46328</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="51" t="s">
-        <v>47</v>
+      <c r="G18" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1043,7 +1052,7 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="18"/>
       <c r="B20" s="15"/>
-      <c r="C20" s="52">
+      <c r="C20" s="51">
         <v>10</v>
       </c>
       <c r="D20" s="22" t="s">
@@ -1057,7 +1066,7 @@
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I20" s="8"/>
     </row>
@@ -1080,7 +1089,7 @@
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="14"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="52">
+      <c r="C22" s="51">
         <v>11</v>
       </c>
       <c r="D22" s="22" t="s">
@@ -1108,7 +1117,7 @@
         <v>46344</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="39"/>
@@ -1120,23 +1129,23 @@
       <c r="B24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="51">
         <v>12</v>
       </c>
-      <c r="D24" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="49">
+      <c r="D24" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="48">
         <v>46349</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="51" t="s">
-        <v>49</v>
+      <c r="G24" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1162,7 +1171,7 @@
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
-      <c r="C26" s="52">
+      <c r="C26" s="51">
         <v>13</v>
       </c>
       <c r="D26" s="22" t="s">
@@ -1172,11 +1181,11 @@
         <v>46356</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1190,7 +1199,7 @@
         <v>46358</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="39"/>
@@ -1198,7 +1207,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="14"/>
       <c r="B28" s="15"/>
-      <c r="C28" s="52">
+      <c r="C28" s="51">
         <v>14</v>
       </c>
       <c r="D28" s="22" t="s">
@@ -1208,7 +1217,7 @@
         <v>46363</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="24"/>
@@ -1224,7 +1233,7 @@
         <v>46365</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="39"/>
@@ -1236,21 +1245,21 @@
       <c r="B30" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="51">
         <v>15</v>
       </c>
-      <c r="D30" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="49">
+      <c r="D30" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="48">
         <v>46370</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="G30" s="50"/>
-      <c r="H30" s="51" t="s">
-        <v>51</v>
+      <c r="G30" s="49"/>
+      <c r="H30" s="50" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1260,7 +1269,7 @@
       <c r="D31" s="41"/>
       <c r="E31" s="38"/>
       <c r="F31" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G31" s="42"/>
       <c r="H31" s="39"/>
@@ -1270,12 +1279,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1285,6 +1288,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/website-SDS-CSC109/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9743D8-50DA-704E-BECB-441F13BEA724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E8348A1A-7C9E-0D41-80F9-C4AE4A7F34CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Storytelling</t>
   </si>
   <si>
-    <t>Tableau</t>
-  </si>
-  <si>
     <t>Persuasive Visualization</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>a3p2: Print Vis Critique/Reflection</t>
   </si>
   <si>
-    <t>a3p1: Digital Vis</t>
-  </si>
-  <si>
     <t>a4p2: Digital Vis Critique/Reflection</t>
   </si>
   <si>
@@ -197,6 +191,15 @@
   </si>
   <si>
     <t>NO CLASS -MOUNTAIN DAY</t>
+  </si>
+  <si>
+    <t>In-class work day a3p1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableau Tutorial (on your own) </t>
+  </si>
+  <si>
+    <t>a4p1: Digital Vis</t>
   </si>
 </sst>
 </file>
@@ -368,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -446,15 +449,6 @@
     <xf numFmtId="16" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -462,6 +456,17 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,7 +723,7 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="14"/>
       <c r="B2" s="15"/>
-      <c r="C2" s="51">
+      <c r="C2" s="56">
         <v>1</v>
       </c>
       <c r="D2" s="22"/>
@@ -730,7 +735,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="52"/>
+      <c r="C3" s="58"/>
       <c r="D3" s="25" t="s">
         <v>13</v>
       </c>
@@ -741,14 +746,14 @@
         <v>10</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="18"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="51">
+      <c r="C4" s="56">
         <v>2</v>
       </c>
       <c r="D4" s="22" t="s">
@@ -766,7 +771,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="52"/>
+      <c r="C5" s="58"/>
       <c r="D5" s="25" t="s">
         <v>13</v>
       </c>
@@ -777,16 +782,16 @@
         <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="18"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="51">
+      <c r="C6" s="56">
         <v>3</v>
       </c>
       <c r="D6" s="22" t="s">
@@ -808,27 +813,27 @@
       <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="55">
+      <c r="C7" s="58"/>
+      <c r="D7" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="52">
         <v>46288</v>
       </c>
-      <c r="F7" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>43</v>
+      <c r="F7" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="18"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="51">
+      <c r="C8" s="56">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
@@ -846,7 +851,7 @@
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="52"/>
+      <c r="C9" s="58"/>
       <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
@@ -862,7 +867,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="14"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="51">
+      <c r="C10" s="56">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
@@ -884,7 +889,7 @@
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="52"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="43" t="s">
         <v>13</v>
       </c>
@@ -895,10 +900,10 @@
         <v>23</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -908,7 +913,7 @@
       <c r="B12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="56">
         <v>6</v>
       </c>
       <c r="D12" s="11" t="s">
@@ -926,7 +931,7 @@
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="52"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="25" t="s">
         <v>13</v>
       </c>
@@ -937,13 +942,13 @@
         <v>24</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="14"/>
       <c r="B14" s="15"/>
-      <c r="C14" s="51">
+      <c r="C14" s="56">
         <v>7</v>
       </c>
       <c r="D14" s="22" t="s">
@@ -959,24 +964,29 @@
       <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="26">
+      <c r="A15" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="58"/>
+      <c r="D15" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="52">
         <v>46316</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="27"/>
+      <c r="F15" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="59"/>
+      <c r="H15" s="60"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="14"/>
       <c r="B16" s="15"/>
-      <c r="C16" s="51">
+      <c r="C16" s="56">
         <v>8</v>
       </c>
       <c r="D16" s="22" t="s">
@@ -994,7 +1004,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="52"/>
+      <c r="C17" s="58"/>
       <c r="D17" s="25" t="s">
         <v>13</v>
       </c>
@@ -1002,7 +1012,7 @@
         <v>46323</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="H17" s="27"/>
     </row>
@@ -1013,7 +1023,7 @@
       <c r="B18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="56">
         <v>9</v>
       </c>
       <c r="D18" s="47" t="s">
@@ -1023,19 +1033,19 @@
         <v>46328</v>
       </c>
       <c r="F18" s="49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="53"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="37" t="s">
         <v>13</v>
       </c>
@@ -1043,7 +1053,7 @@
         <v>46330</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="39"/>
@@ -1052,7 +1062,7 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="18"/>
       <c r="B20" s="15"/>
-      <c r="C20" s="51">
+      <c r="C20" s="56">
         <v>10</v>
       </c>
       <c r="D20" s="22" t="s">
@@ -1062,18 +1072,18 @@
         <v>46335</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="53"/>
+      <c r="C21" s="57"/>
       <c r="D21" s="37" t="s">
         <v>13</v>
       </c>
@@ -1081,7 +1091,7 @@
         <v>46337</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="39"/>
@@ -1089,7 +1099,7 @@
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="14"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="51">
+      <c r="C22" s="56">
         <v>11</v>
       </c>
       <c r="D22" s="22" t="s">
@@ -1109,7 +1119,7 @@
       <c r="B23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="53"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="37" t="s">
         <v>13</v>
       </c>
@@ -1117,7 +1127,7 @@
         <v>46344</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="39"/>
@@ -1129,7 +1139,7 @@
       <c r="B24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="56">
         <v>12</v>
       </c>
       <c r="D24" s="47" t="s">
@@ -1139,13 +1149,13 @@
         <v>46349</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1155,7 +1165,7 @@
       <c r="B25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="53"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="32" t="s">
         <v>13</v>
       </c>
@@ -1171,7 +1181,7 @@
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
-      <c r="C26" s="51">
+      <c r="C26" s="56">
         <v>13</v>
       </c>
       <c r="D26" s="22" t="s">
@@ -1181,17 +1191,17 @@
         <v>46356</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="20"/>
-      <c r="C27" s="53"/>
+      <c r="C27" s="57"/>
       <c r="D27" s="37" t="s">
         <v>13</v>
       </c>
@@ -1199,7 +1209,7 @@
         <v>46358</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="39"/>
@@ -1207,7 +1217,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="14"/>
       <c r="B28" s="15"/>
-      <c r="C28" s="51">
+      <c r="C28" s="56">
         <v>14</v>
       </c>
       <c r="D28" s="22" t="s">
@@ -1217,7 +1227,7 @@
         <v>46363</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="24"/>
@@ -1225,7 +1235,7 @@
     <row r="29" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="53"/>
+      <c r="C29" s="57"/>
       <c r="D29" s="37" t="s">
         <v>13</v>
       </c>
@@ -1233,7 +1243,7 @@
         <v>46365</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="39"/>
@@ -1245,7 +1255,7 @@
       <c r="B30" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="56">
         <v>15</v>
       </c>
       <c r="D30" s="47" t="s">
@@ -1255,21 +1265,21 @@
         <v>46370</v>
       </c>
       <c r="F30" s="49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G30" s="49"/>
       <c r="H30" s="50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="53"/>
+      <c r="C31" s="57"/>
       <c r="D31" s="41"/>
       <c r="E31" s="38"/>
       <c r="F31" s="20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G31" s="42"/>
       <c r="H31" s="39"/>
@@ -1279,6 +1289,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1288,12 +1304,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E8348A1A-7C9E-0D41-80F9-C4AE4A7F34CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1725383-A7F4-D34D-B1A2-58EBD8F3B6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,13 +193,13 @@
     <t>NO CLASS -MOUNTAIN DAY</t>
   </si>
   <si>
-    <t>In-class work day a3p1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tableau Tutorial (on your own) </t>
   </si>
   <si>
     <t>a4p1: Digital Vis</t>
+  </si>
+  <si>
+    <t>In-class work day a4p1</t>
   </si>
 </sst>
 </file>
@@ -456,17 +456,17 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,7 +723,7 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="14"/>
       <c r="B2" s="15"/>
-      <c r="C2" s="56">
+      <c r="C2" s="58">
         <v>1</v>
       </c>
       <c r="D2" s="22"/>
@@ -735,7 +735,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="58"/>
+      <c r="C3" s="59"/>
       <c r="D3" s="25" t="s">
         <v>13</v>
       </c>
@@ -753,7 +753,7 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="18"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="56">
+      <c r="C4" s="58">
         <v>2</v>
       </c>
       <c r="D4" s="22" t="s">
@@ -771,7 +771,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="58"/>
+      <c r="C5" s="59"/>
       <c r="D5" s="25" t="s">
         <v>13</v>
       </c>
@@ -791,7 +791,7 @@
     <row r="6" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="18"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="56">
+      <c r="C6" s="58">
         <v>3</v>
       </c>
       <c r="D6" s="22" t="s">
@@ -813,7 +813,7 @@
       <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="58"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="51" t="s">
         <v>13</v>
       </c>
@@ -833,7 +833,7 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="18"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="56">
+      <c r="C8" s="58">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
@@ -851,7 +851,7 @@
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="58"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
@@ -867,7 +867,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="14"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="56">
+      <c r="C10" s="58">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
@@ -889,7 +889,7 @@
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="58"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="43" t="s">
         <v>13</v>
       </c>
@@ -913,7 +913,7 @@
       <c r="B12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="58">
         <v>6</v>
       </c>
       <c r="D12" s="11" t="s">
@@ -931,7 +931,7 @@
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="58"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="25" t="s">
         <v>13</v>
       </c>
@@ -948,7 +948,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="14"/>
       <c r="B14" s="15"/>
-      <c r="C14" s="56">
+      <c r="C14" s="58">
         <v>7</v>
       </c>
       <c r="D14" s="22" t="s">
@@ -970,7 +970,7 @@
       <c r="B15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="51" t="s">
         <v>13</v>
       </c>
@@ -978,15 +978,15 @@
         <v>46316</v>
       </c>
       <c r="F15" s="54" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60"/>
+        <v>53</v>
+      </c>
+      <c r="G15" s="56"/>
+      <c r="H15" s="57"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="14"/>
       <c r="B16" s="15"/>
-      <c r="C16" s="56">
+      <c r="C16" s="58">
         <v>8</v>
       </c>
       <c r="D16" s="22" t="s">
@@ -1004,7 +1004,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="58"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="25" t="s">
         <v>13</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>46323</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H17" s="27"/>
     </row>
@@ -1023,7 +1023,7 @@
       <c r="B18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="58">
         <v>9</v>
       </c>
       <c r="D18" s="47" t="s">
@@ -1039,13 +1039,13 @@
         <v>39</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="57"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="37" t="s">
         <v>13</v>
       </c>
@@ -1062,7 +1062,7 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="18"/>
       <c r="B20" s="15"/>
-      <c r="C20" s="56">
+      <c r="C20" s="58">
         <v>10</v>
       </c>
       <c r="D20" s="22" t="s">
@@ -1083,7 +1083,7 @@
     <row r="21" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="57"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="37" t="s">
         <v>13</v>
       </c>
@@ -1099,7 +1099,7 @@
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="14"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="56">
+      <c r="C22" s="58">
         <v>11</v>
       </c>
       <c r="D22" s="22" t="s">
@@ -1119,7 +1119,7 @@
       <c r="B23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="57"/>
+      <c r="C23" s="60"/>
       <c r="D23" s="37" t="s">
         <v>13</v>
       </c>
@@ -1139,7 +1139,7 @@
       <c r="B24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="58">
         <v>12</v>
       </c>
       <c r="D24" s="47" t="s">
@@ -1165,7 +1165,7 @@
       <c r="B25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="57"/>
+      <c r="C25" s="60"/>
       <c r="D25" s="32" t="s">
         <v>13</v>
       </c>
@@ -1181,7 +1181,7 @@
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
-      <c r="C26" s="56">
+      <c r="C26" s="58">
         <v>13</v>
       </c>
       <c r="D26" s="22" t="s">
@@ -1201,7 +1201,7 @@
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="20"/>
-      <c r="C27" s="57"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="37" t="s">
         <v>13</v>
       </c>
@@ -1217,7 +1217,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="14"/>
       <c r="B28" s="15"/>
-      <c r="C28" s="56">
+      <c r="C28" s="58">
         <v>14</v>
       </c>
       <c r="D28" s="22" t="s">
@@ -1235,7 +1235,7 @@
     <row r="29" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="57"/>
+      <c r="C29" s="60"/>
       <c r="D29" s="37" t="s">
         <v>13</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="B30" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="58">
         <v>15</v>
       </c>
       <c r="D30" s="47" t="s">
@@ -1275,7 +1275,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="57"/>
+      <c r="C31" s="60"/>
       <c r="D31" s="41"/>
       <c r="E31" s="38"/>
       <c r="F31" s="20" t="s">
@@ -1289,12 +1289,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1304,6 +1298,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
